--- a/AI Audit Log_NguyenHoanAnhQuan.xlsx
+++ b/AI Audit Log_NguyenHoanAnhQuan.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUMMER2026\SWD392_SU26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BCD105-D2D2-4569-A0E9-368A402371F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26BA4C5-0218-4770-9EFE-9EED970EDF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week3.1" sheetId="3" r:id="rId3"/>
+    <sheet name="Week3.2" sheetId="5" r:id="rId4"/>
+    <sheet name="Assignment 3" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="86">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -157,6 +158,201 @@
     <t>Phản hồi: AI cho biết use case giúp xác định yêu cầu, giao tiếp giữa stakeholder và dev, và làm cơ sở thiết kế.
 Kiểm chứng: Tôi đối chiếu với tài liệu SE và thấy đúng.
 Quyết định: Xác định Use Case là bước quan trọng trước khi thiết kế hệ thống.</t>
+  </si>
+  <si>
+    <t>Static Modeling</t>
+  </si>
+  <si>
+    <t>“Static Modeling là gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Static Modeling là mô hình hóa cấu trúc tĩnh của hệ thống, mô tả các lớp, thuộc tính, quan hệ và thao tác của lớp bằng UML Class Diagram.
+Kiểm chứng: Tôi đối chiếu với slide và thấy nội dung đúng với phần “Overview – Static Modeling”.
+Quyết định: Sử dụng khái niệm này để hiểu nền tảng của UML Class Diagram trong phân tích thiết kế hệ thống.</t>
+  </si>
+  <si>
+    <t>Objects &amp; Classes</t>
+  </si>
+  <si>
+    <t>“Phân biệt Object và Class bằng ví dụ đơn giản”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Object là một đối tượng cụ thể trong thực tế, còn Class là tập hợp các object có cùng đặc điểm. AI đưa ví dụ Employee và Account để minh họa.
+Kiểm chứng: Tôi so sánh với ví dụ trong slide và thấy trùng khớp với nội dung bài học.
+Quyết định: Dùng cách phân biệt này để giải thích khi thuyết trình UML.</t>
+  </si>
+  <si>
+    <t>Attributes</t>
+  </si>
+  <si>
+    <t>“Attribute trong Class Diagram là gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết Attribute là dữ liệu của object trong class, ví dụ accountNumber hoặc balance.
+Kiểm chứng: Tôi kiểm tra lại slide phần Objects and Classes và thấy đúng với định nghĩa của giáo viên.
+Quyết định: Áp dụng khi thiết kế các class entity cho dự án.</t>
+  </si>
+  <si>
+    <t>Association Between Classes</t>
+  </si>
+  <si>
+    <t>“Association giữa các class là gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Association là mối quan hệ giữa hai hoặc nhiều class, ví dụ Employee works in Department. AI cũng giải thích link là quan hệ giữa các object cụ thể.
+Kiểm chứng: Tôi đọc lại phần Association Between Classes trong slide và thấy đúng định nghĩa UML.
+Quyết định: Sử dụng Association để xác định các quan hệ trong class diagram của dự án.</t>
+  </si>
+  <si>
+    <t>UML Association Notation</t>
+  </si>
+  <si>
+    <t>“Ký hiệu Association trong UML được vẽ như thế nào?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả Association được biểu diễn bằng đường nối giữa các class và có thể thêm multiplicity như 1..*, 0..1.
+Kiểm chứng: Tôi đối chiếu với hình UML notation trong slide và thấy đúng.
+Quyết định: Áp dụng các ký hiệu multiplicity đúng chuẩn khi vẽ UML.</t>
+  </si>
+  <si>
+    <t>Association Class</t>
+  </si>
+  <si>
+    <t>“Association Class dùng để làm gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Association Class dùng khi mối quan hệ giữa các class có thuộc tính riêng, thường xuất hiện trong many-to-many relationship.
+Kiểm chứng: Tôi so sánh với ví dụ Project – Employee trong slide và thấy đúng.
+Quyết định: Áp dụng cho các bảng trung gian như OrderDetail hoặc Enrollment trong database.</t>
+  </si>
+  <si>
+    <t>Composition &amp; Aggregation</t>
+  </si>
+  <si>
+    <t>“Phân biệt Composition và Aggregation”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Composition là quan hệ whole-part mạnh, part sống và chết cùng whole; còn Aggregation là quan hệ yếu hơn, part có thể tồn tại độc lập.
+Kiểm chứng: Tôi đối chiếu với nội dung slide phần Composition &amp; Aggregation Hierarchies và thấy đúng.
+Quyết định: Sử dụng Composition cho các thành phần phụ thuộc hoàn toàn vào object chính.</t>
+  </si>
+  <si>
+    <t>Inheritance</t>
+  </si>
+  <si>
+    <t>“Subclass kế thừa gì từ superclass?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết subclass kế thừa thuộc tính và operation từ superclass nhưng có thể mở rộng thêm chức năng riêng.
+Kiểm chứng: Tôi đối chiếu với phần “Inheritance of Class Attributes/Operations” trong slide.
+Quyết định: Dùng inheritance để tránh lặp code và mô hình hóa hệ thống rõ ràng hơn.</t>
+  </si>
+  <si>
+    <t>Context Modeling</t>
+  </si>
+  <si>
+    <t>“Context Modeling giúp ích gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Context Modeling giúp xác định phạm vi hệ thống, phân biệt thành phần bên trong và bên ngoài hệ thống.
+Kiểm chứng: Tôi kiểm tra phần Context Modeling trong slide và thấy nội dung đúng.
+Quyết định: Áp dụng để xác định boundary của hệ thống khi phân tích yêu cầu.</t>
+  </si>
+  <si>
+    <t>System Context Diagram</t>
+  </si>
+  <si>
+    <t>“System Context Diagram là gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích đây là sơ đồ mô tả ranh giới giữa hệ thống và môi trường bên ngoài, hệ thống được xem như black box.
+Kiểm chứng: Tôi đối chiếu với hình minh họa trong slide và thấy đúng.
+Quyết định: Sử dụng sơ đồ context trước khi thiết kế chi tiết hệ thống.</t>
+  </si>
+  <si>
+    <t>External Classes</t>
+  </si>
+  <si>
+    <t>“External classes là gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích external classes là các thành phần bên ngoài hệ thống như external device, external system hoặc timer.
+Kiểm chứng: Tôi đối chiếu với phần Modeling External Classes trong slide và thấy đúng.
+Quyết định: Dùng để xác định actor và thiết bị tương tác với hệ thống.</t>
+  </si>
+  <si>
+    <t>Entity Classes</t>
+  </si>
+  <si>
+    <t>“Entity class có vai trò gì trong hệ thống?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Entity class dùng để lưu trữ dữ liệu và cung cấp quyền truy cập dữ liệu, thường là các class persistent.
+Kiểm chứng: Tôi kiểm tra phần Static Modeling of Entity Classes trong slide và thấy đúng nội dung.
+Quyết định: Áp dụng để xác định các bảng dữ liệu chính trong dự án phần mềm.</t>
+  </si>
+  <si>
+    <t>UML Notation</t>
+  </si>
+  <si>
+    <t>“Ký hiệu UML chuẩn cho class diagram gồm những gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả class gồm tên class, attributes, operations và các đường quan hệ như association, aggregation, composition, inheritance.
+Kiểm chứng: Tôi đối chiếu với hình UML notation trong slide bài giảng.
+Quyết định: Sử dụng đúng ký hiệu UML chuẩn khi vẽ bằng draw.io hoặc PlantUML.</t>
+  </si>
+  <si>
+    <t>“Hệ thống của nhóm có những external classes nào?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất external classes như Display Screen, Payment System, AI Engine, SMS Gateway.
+Kiểm chứng: Tôi so sánh với mô hình context diagram đã phân tích trước đó.
+Quyết định: Thêm các external system vào sơ đồ để mô tả tương tác hệ thống đầy đủ hơn.</t>
+  </si>
+  <si>
+    <t>Multiplicity</t>
+  </si>
+  <si>
+    <t>“Multiplicity trong class diagram được xác định như thế nào?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích các ký hiệu 1..1, 1.., 0.. và ví dụ một Queue có nhiều Ticket.
+Kiểm chứng: Tôi đối chiếu với ký hiệu UML trong slide.
+Quyết định: Sử dụng multiplicity để biểu diễn số lượng đối tượng trong quan hệ.</t>
+  </si>
+  <si>
+    <t>Operations/Methods</t>
+  </si>
+  <si>
+    <t>“Mỗi class nên có phương thức gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các method như createTicket(), callNextQueue(), sendNotification(), login().
+Kiểm chứng: Tôi đối chiếu với chức năng hệ thống mà nhóm đã phân tích.
+Quyết định: Dùng các operation này để thể hiện hành vi của class trong UML.</t>
+  </si>
+  <si>
+    <t>PlantUML</t>
+  </si>
+  <si>
+    <t>“Hãy tạo code PlantUML cho class diagram của nhóm tôi”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh code PlantUML gồm các class, thuộc tính và quan hệ giữa các class.
+Kiểm chứng: Tôi copy code vào PlantUML để kiểm tra sơ đồ hiển thị đúng.
+Quyết định: Dùng PlantUML để chỉnh sửa và hoàn thiện class diagram của nhóm.</t>
+  </si>
+  <si>
+    <t>Kiểm tra &amp; hoàn thiện</t>
+  </si>
+  <si>
+    <t>“Kiểm tra giúp tôi class diagram đã đúng chuẩn UML chưa”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI kiểm tra các lỗi như thiếu multiplicity, sai quan hệ inheritance hoặc dùng sai composition/aggregation.
+Kiểm chứng: Tôi so sánh lại với slide UML và góp ý của giảng viên trên lớp.
+Quyết định: Chỉnh sửa sơ đồ theo góp ý để hoàn thiện bản cuối cùng nộp nhóm.</t>
   </si>
 </sst>
 </file>
@@ -216,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -238,6 +434,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -668,7 +867,7 @@
     <col min="4" max="4" width="44.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.9">
+    <row r="1" spans="1:4" ht="27.75">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -678,7 +877,7 @@
       <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -816,14 +1015,323 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="47.75" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="3" max="3" width="54.3125" customWidth="1"/>
+    <col min="4" max="4" width="77.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="47.75" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="81.75" customHeight="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="67.5" customHeight="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="47.75" customHeight="1">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="61.9" customHeight="1">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="66" customHeight="1">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="72.75" customHeight="1">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="91.15" customHeight="1">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="91.15" customHeight="1">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="91.15" customHeight="1">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="91.15" customHeight="1">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="91.15" customHeight="1">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="77.25" customHeight="1">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2795E5-0A07-4918-BFC6-ED555F7A394E}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="8.9375" customWidth="1"/>
+    <col min="2" max="2" width="32.5" customWidth="1"/>
+    <col min="3" max="3" width="26.375" customWidth="1"/>
+    <col min="4" max="4" width="58.8125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="13.9">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="87" customHeight="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="74.349999999999994" customHeight="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="73.5" customHeight="1">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="90" customHeight="1">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="90" customHeight="1">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="82.5" customHeight="1">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="4.1500000000000004" customHeight="1"/>
+    <row r="12" spans="1:4" hidden="1"/>
+    <row r="13" spans="1:4" hidden="1"/>
+    <row r="14" spans="1:4" hidden="1"/>
+    <row r="15" spans="1:4" hidden="1"/>
+    <row r="16" spans="1:4" hidden="1"/>
+    <row r="17" hidden="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/AI Audit Log_NguyenHoanAnhQuan.xlsx
+++ b/AI Audit Log_NguyenHoanAnhQuan.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUMMER2026\SWD392_SU26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26BA4C5-0218-4770-9EFE-9EED970EDF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8061E323-C529-41FF-8153-FA2E94473AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" r:id="rId2"/>
     <sheet name="Week3.1" sheetId="3" r:id="rId3"/>
     <sheet name="Week3.2" sheetId="5" r:id="rId4"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId5"/>
+    <sheet name="Week4.1" sheetId="6" r:id="rId5"/>
+    <sheet name="Week4.2" sheetId="7" r:id="rId6"/>
+    <sheet name="Assignment 3" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="129">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -353,19 +355,185 @@
     <t>Phản hồi: AI kiểm tra các lỗi như thiếu multiplicity, sai quan hệ inheritance hoặc dùng sai composition/aggregation.
 Kiểm chứng: Tôi so sánh lại với slide UML và góp ý của giảng viên trên lớp.
 Quyết định: Chỉnh sửa sơ đồ theo góp ý để hoàn thiện bản cuối cùng nộp nhóm.</t>
+  </si>
+  <si>
+    <t>Xác định Class</t>
+  </si>
+  <si>
+    <t>"Đối với hệ thống Smart Queue Management System Using AI, các class chính nên gồm những gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các class User, Queue, Ticket, ServiceCounter, QueuePredictionAI, Notification, Feedback.
+Kiểm chứng: Tôi đối chiếu với chức năng của hệ thống đã phân tích trước đó.
+Quyết định: Chọn các class phù hợp để xây dựng class diagram.</t>
+  </si>
+  <si>
+    <t>Entity Class</t>
+  </si>
+  <si>
+    <t>"Những class nào nên được đánh dấu là Entity Class?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác định User, Queue, Ticket, Appointment, Feedback là các entity class vì lưu trữ dữ liệu lâu dài.
+Kiểm chứng: So sánh với lý thuyết Entity Class trong slide.
+Quyết định: Áp dụng stereotype «entity» cho các class này.</t>
+  </si>
+  <si>
+    <t>Association</t>
+  </si>
+  <si>
+    <t>"Mối quan hệ giữa User và Ticket nên được mô hình hóa như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Association 1 User có thể sở hữu nhiều Ticket.
+Kiểm chứng: Đối chiếu với quy trình lấy số thứ tự của khách hàng.
+Quyết định: Sử dụng multiplicity 1..* trong sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Multiplicity giữa Queue và Ticket là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: Một Queue chứa nhiều Ticket, mỗi Ticket chỉ thuộc một Queue.
+Kiểm chứng: Đúng với nghiệp vụ hàng chờ.
+Quyết định: Áp dụng 1..* giữa Queue và Ticket.</t>
+  </si>
+  <si>
+    <t>Composition</t>
+  </si>
+  <si>
+    <t>"Queue và Ticket nên dùng Association hay Composition?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Composition vì Ticket không tồn tại nếu Queue bị xóa.
+Kiểm chứng: Đối chiếu với khái niệm Composition trong bài học.
+Quyết định: Dùng Composition trong UML.</t>
+  </si>
+  <si>
+    <t>"Có thể sử dụng kế thừa trong hệ thống này không?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất User là superclass, Customer và Staff là subclasses.
+Kiểm chứng: Kiểm tra với chức năng của từng loại người dùng.
+Quyết định: Áp dụng Generalization/Specialization.</t>
+  </si>
+  <si>
+    <t>Kiểm tra UML</t>
+  </si>
+  <si>
+    <t>"Class Diagram hiện tại có thiếu quan hệ nào không?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện thiếu quan hệ giữa ServiceCounter và Queue.
+Kiểm chứng: Đối chiếu với luồng phục vụ khách hàng.
+Quyết định: Bổ sung quan hệ còn thiếu vào sơ đồ.</t>
+  </si>
+  <si>
+    <t>Dynamic Modeling</t>
+  </si>
+  <si>
+    <t>"Dynamic Modeling là gì trong UML?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Dynamic Modeling mô tả hành vi động của hệ thống, tập trung vào luồng điều khiển và tương tác giữa các đối tượng theo thời gian.
+Kiểm chứng: Tôi đối chiếu với slide Ch09-11 và thấy phù hợp với định nghĩa của bài học.
+Quyết định: Sử dụng khái niệm này để phân biệt với Static Modeling đã học trước đó.</t>
+  </si>
+  <si>
+    <t>Dynamic Interaction Modeling</t>
+  </si>
+  <si>
+    <t>"Dynamic Interaction Modeling dùng để làm gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết Dynamic Interaction Modeling được sử dụng để mô tả cách các object tương tác nhằm hiện thực hóa Use Case.
+Kiểm chứng: Tôi đối chiếu với phần Dynamic Interaction Modeling trong slide.
+Quyết định: Áp dụng khi phân tích các Use Case của dự án nhóm.</t>
+  </si>
+  <si>
+    <t>Communication Diagram</t>
+  </si>
+  <si>
+    <t>"Communication Diagram là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích đây là sơ đồ UML mô tả sự tương tác giữa các object thông qua các message và số thứ tự message.
+Kiểm chứng: Tôi đối chiếu với định nghĩa trong slide.
+Quyết định: Sử dụng Communication Diagram để mô tả tương tác trong hệ thống.</t>
+  </si>
+  <si>
+    <t>Sequence Diagram</t>
+  </si>
+  <si>
+    <t>"Sequence Diagram là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Sequence Diagram thể hiện thứ tự gửi nhận message giữa các object theo thời gian từ trên xuống dưới.
+Kiểm chứng: So sánh với ví dụ View Alarms trong slide.
+Quyết định: Dùng Sequence Diagram để mô tả luồng xử lý chính của hệ thống.</t>
+  </si>
+  <si>
+    <t>Sequence vs Communication</t>
+  </si>
+  <si>
+    <t>"Sự khác nhau giữa Sequence Diagram và Communication Diagram?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết Sequence Diagram nhấn mạnh yếu tố thời gian còn Communication Diagram nhấn mạnh mối liên kết giữa các object.
+Kiểm chứng: Đối chiếu với bảng so sánh trong slide.
+Quyết định: Hiểu ưu điểm của từng loại sơ đồ để sử dụng phù hợp.</t>
+  </si>
+  <si>
+    <t>UC Realization</t>
+  </si>
+  <si>
+    <t>"Làm thế nào để xây dựng Sequence Diagram từ Use Case?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất xác định actor, boundary object, control object và message sequence.
+Kiểm chứng: So sánh với quy trình trong bài học.
+Quyết định: Áp dụng cho Use Case của dự án Smart Queue Management System.</t>
+  </si>
+  <si>
+    <t>Main Scenario</t>
+  </si>
+  <si>
+    <t>"Main Sequence trong Dynamic Modeling là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích đây là luồng xử lý chính của Use Case khi mọi điều kiện đều thành công.
+Kiểm chứng: Đối chiếu với ví dụ Make Order Request.
+Quyết định: Sử dụng để xây dựng Sequence Diagram chính.</t>
+  </si>
+  <si>
+    <t>Alternative Scenario</t>
+  </si>
+  <si>
+    <t>"Alternative Sequence được biểu diễn như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích đây là các luồng xử lý thay thế khi có ngoại lệ hoặc điều kiện khác xảy ra.
+Kiểm chứng: So sánh với trường hợp Credit Card Denied trong slide.
+Quyết định: Bổ sung các nhánh thay thế vào Sequence Diagram.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -412,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -426,7 +594,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -434,6 +602,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -773,15 +953,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.9375" customWidth="1"/>
-    <col min="2" max="2" width="26.875" customWidth="1"/>
-    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="1" max="1" width="20.9296875" customWidth="1"/>
+    <col min="2" max="2" width="26.86328125" customWidth="1"/>
+    <col min="3" max="3" width="24.265625" customWidth="1"/>
     <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.9">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -796,7 +976,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="67.5">
+    <row r="2" spans="1:5" ht="71.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -810,7 +990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="54">
+    <row r="3" spans="1:5" ht="57">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -824,7 +1004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="67.5">
+    <row r="4" spans="1:5" ht="71.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -838,7 +1018,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="81">
+    <row r="5" spans="1:5" ht="85.5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -860,14 +1040,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="41.9375" customWidth="1"/>
-    <col min="3" max="3" width="45.8125" customWidth="1"/>
-    <col min="4" max="4" width="44.875" customWidth="1"/>
+    <col min="2" max="2" width="41.9296875" customWidth="1"/>
+    <col min="3" max="3" width="45.796875" customWidth="1"/>
+    <col min="4" max="4" width="44.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.75">
+    <row r="1" spans="1:4" ht="28.5">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1018,9 +1198,9 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="47.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="22.875" customWidth="1"/>
-    <col min="3" max="3" width="54.3125" customWidth="1"/>
-    <col min="4" max="4" width="77.5" customWidth="1"/>
+    <col min="2" max="2" width="22.86328125" customWidth="1"/>
+    <col min="3" max="3" width="54.33203125" customWidth="1"/>
+    <col min="4" max="4" width="77.46484375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="47.75" customHeight="1">
@@ -1213,15 +1393,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2795E5-0A07-4918-BFC6-ED555F7A394E}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.9375" customWidth="1"/>
-    <col min="2" max="2" width="32.5" customWidth="1"/>
-    <col min="3" max="3" width="26.375" customWidth="1"/>
-    <col min="4" max="4" width="58.8125" customWidth="1"/>
+    <col min="1" max="1" width="8.9296875" customWidth="1"/>
+    <col min="2" max="2" width="32.46484375" customWidth="1"/>
+    <col min="3" max="3" width="26.3984375" customWidth="1"/>
+    <col min="4" max="4" width="58.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.9">
+    <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1332,9 +1512,291 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D2BBFF-A5A9-4621-A1B0-B5B41A144524}">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="9.19921875" customWidth="1"/>
+    <col min="2" max="2" width="34.06640625" customWidth="1"/>
+    <col min="3" max="3" width="41.796875" customWidth="1"/>
+    <col min="4" max="4" width="47.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="118.25" customHeight="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="134.35" customHeight="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="96.4" customHeight="1">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="96.4" customHeight="1">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="96.4" customHeight="1">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="96.4" customHeight="1">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="96.4" customHeight="1">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" ht="12.75" customHeight="1"/>
+    <row r="18" hidden="1"/>
+    <row r="19" hidden="1"/>
+    <row r="20" hidden="1"/>
+    <row r="21" hidden="1"/>
+    <row r="22" hidden="1"/>
+    <row r="23" hidden="1"/>
+    <row r="24" hidden="1"/>
+    <row r="25" hidden="1"/>
+    <row r="26" hidden="1"/>
+    <row r="27" hidden="1"/>
+    <row r="28" hidden="1"/>
+    <row r="29" hidden="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966BDC56-E696-48BC-BCCD-FDFD9FA85D73}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="36.33203125" customWidth="1"/>
+    <col min="3" max="3" width="30.3984375" customWidth="1"/>
+    <col min="4" max="4" width="44.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="107.65" customHeight="1">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="108.75" customHeight="1">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="118.5" customHeight="1">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="99.4" customHeight="1">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="113.25" customHeight="1">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="97.5" customHeight="1">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="88.5" customHeight="1">
+      <c r="A8" s="12">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="103.9" customHeight="1">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AI Audit Log_NguyenHoanAnhQuan.xlsx
+++ b/AI Audit Log_NguyenHoanAnhQuan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUMMER2026\SWD392_SU26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8061E323-C529-41FF-8153-FA2E94473AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7CA1C6-97EE-4921-8EEA-C28B59543728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="7" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Week3.2" sheetId="5" r:id="rId4"/>
     <sheet name="Week4.1" sheetId="6" r:id="rId5"/>
     <sheet name="Week4.2" sheetId="7" r:id="rId6"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId7"/>
+    <sheet name="Week5" sheetId="8" r:id="rId7"/>
+    <sheet name="Assignment 3" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="158">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -514,6 +515,111 @@
     <t>Phản hồi: AI giải thích đây là các luồng xử lý thay thế khi có ngoại lệ hoặc điều kiện khác xảy ra.
 Kiểm chứng: So sánh với trường hợp Credit Card Denied trong slide.
 Quyết định: Bổ sung các nhánh thay thế vào Sequence Diagram.</t>
+  </si>
+  <si>
+    <t>Xác định Use Case</t>
+  </si>
+  <si>
+    <t>"Đối với hệ thống Smart Queue Management System Using AI, những Use Case nào cần Sequence Diagram?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các Use Case như Book Queue Ticket, Check Queue Status, Call Next Customer, Send Notification và Cancel Queue.
+Kiểm chứng: Tôi đối chiếu với Use Case Diagram của nhóm.
+Quyết định: Chọn các Use Case quan trọng để xây dựng Sequence Diagram.</t>
+  </si>
+  <si>
+    <t>Xác định đối tượng tham gia</t>
+  </si>
+  <si>
+    <t>"Sequence Diagram của Use Case Book Queue Ticket gồm những object nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Customer, Mobile App, QueueController, QueueService, Ticket và NotificationService.
+Kiểm chứng: Tôi so sánh với Class Diagram của nhóm.
+Quyết định: Sử dụng các object này trong sơ đồ.</t>
+  </si>
+  <si>
+    <t>Boundary-Control-Entity</t>
+  </si>
+  <si>
+    <t>"Phân loại các object trong Sequence Diagram theo Boundary, Control và Entity."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác định Mobile App là Boundary, QueueController là Control, Queue và Ticket là Entity.
+Kiểm chứng: Đối chiếu với mô hình BCE đã học.
+Quyết định: Giữ nguyên cách phân loại để đảm bảo thiết kế đúng chuẩn.</t>
+  </si>
+  <si>
+    <t>Message Sequence</t>
+  </si>
+  <si>
+    <t>"Thứ tự các message trong Use Case Book Queue Ticket nên được thực hiện như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất luồng: Customer → Mobile App → QueueController → QueueService → Ticket → NotificationService → Customer.
+Kiểm chứng: Tôi đối chiếu với Main Flow của Use Case Specification.
+Quyết định: Sử dụng thứ tự này để vẽ Sequence Diagram.</t>
+  </si>
+  <si>
+    <t>Alternative Flow</t>
+  </si>
+  <si>
+    <t>"Nếu hàng chờ đã đầy thì Sequence Diagram nên xử lý như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất sử dụng Combined Fragment «alt» với hai nhánh: còn chỗ và đầy hàng chờ.
+Kiểm chứng: So sánh với yêu cầu nghiệp vụ của nhóm.
+Quyết định: Bổ sung nhánh thay thế vào Sequence Diagram.</t>
+  </si>
+  <si>
+    <t>Loop Fragment</t>
+  </si>
+  <si>
+    <t>"Có cần sử dụng loop trong Sequence Diagram không?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất dùng «loop» để kiểm tra liên tục trạng thái hàng chờ hoặc gửi thông báo cho nhiều khách hàng.
+Kiểm chứng: Tôi đối chiếu với ký hiệu UML Sequence Diagram.
+Quyết định: Sử dụng loop khi cần biểu diễn các thao tác lặp.</t>
+  </si>
+  <si>
+    <t>AI Component</t>
+  </si>
+  <si>
+    <t>"QueuePredictionAI nên xuất hiện như thế nào trong Sequence Diagram?"</t>
+  </si>
+  <si>
+    <t>Activation Bar</t>
+  </si>
+  <si>
+    <t>"Activation Bar được sử dụng trong Sequence Diagram như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Activation Bar biểu diễn khoảng thời gian object đang xử lý message.
+Kiểm chứng: Tôi tham khảo ký hiệu UML trong tài liệu học.
+Quyết định: Thêm activation bar để Sequence Diagram dễ hiểu hơn.</t>
+  </si>
+  <si>
+    <t>Return Message</t>
+  </si>
+  <si>
+    <t>"Có cần vẽ return message trong Sequence Diagram không?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích return message có thể được biểu diễn bằng mũi tên nét đứt để thể hiện kết quả trả về.
+Kiểm chứng: So sánh với ví dụ Sequence Diagram trong slide Dynamic Modeling.
+Quyết định: Chỉ thể hiện những return message quan trọng để sơ đồ không quá rối.</t>
+  </si>
+  <si>
+    <t>Kiểm tra sơ đồ</t>
+  </si>
+  <si>
+    <t>"Kiểm tra giúp tôi Sequence Diagram đã đúng với Use Case và Class Diagram chưa."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI kiểm tra tính nhất quán giữa actor, object, message và luồng xử lý; phát hiện một số object chưa có trong Class Diagram và một số message không phù hợp với Main Flow.
+Kiểm chứng: Tôi đối chiếu lại với Use Case Specification và Class Diagram của nhóm.
+Quyết định: Chỉnh sửa Sequence Diagram trước khi hoàn thiện và nộp cho giảng viên.</t>
   </si>
 </sst>
 </file>
@@ -953,15 +1059,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="20.9296875" customWidth="1"/>
-    <col min="2" max="2" width="26.86328125" customWidth="1"/>
-    <col min="3" max="3" width="24.265625" customWidth="1"/>
+    <col min="1" max="1" width="20.9375" customWidth="1"/>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
     <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="13.9">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -976,7 +1082,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="71.25">
+    <row r="2" spans="1:5" ht="67.5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -990,7 +1096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="57">
+    <row r="3" spans="1:5" ht="54">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1004,7 +1110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="71.25">
+    <row r="4" spans="1:5" ht="67.5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1018,7 +1124,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="85.5">
+    <row r="5" spans="1:5" ht="81">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1040,14 +1146,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="41.9296875" customWidth="1"/>
-    <col min="3" max="3" width="45.796875" customWidth="1"/>
-    <col min="4" max="4" width="44.86328125" customWidth="1"/>
+    <col min="2" max="2" width="41.9375" customWidth="1"/>
+    <col min="3" max="3" width="45.8125" customWidth="1"/>
+    <col min="4" max="4" width="44.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.5">
+    <row r="1" spans="1:4" ht="27.75">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1173,20 +1279,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" ht="4.1500000000000004" customHeight="1"/>
-    <row r="20" hidden="1"/>
-    <row r="21" hidden="1"/>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1"/>
-    <row r="24" hidden="1"/>
-    <row r="25" hidden="1"/>
-    <row r="26" hidden="1"/>
-    <row r="27" hidden="1"/>
-    <row r="28" hidden="1"/>
-    <row r="29" hidden="1"/>
-    <row r="30" hidden="1"/>
-    <row r="31" hidden="1"/>
-    <row r="32" hidden="1"/>
+    <row r="19" customFormat="1" ht="4.1500000000000004" customHeight="1"/>
+    <row r="20" customFormat="1" hidden="1"/>
+    <row r="21" customFormat="1" hidden="1"/>
+    <row r="22" customFormat="1" hidden="1"/>
+    <row r="23" customFormat="1" hidden="1"/>
+    <row r="24" customFormat="1" hidden="1"/>
+    <row r="25" customFormat="1" hidden="1"/>
+    <row r="26" customFormat="1" hidden="1"/>
+    <row r="27" customFormat="1" hidden="1"/>
+    <row r="28" customFormat="1" hidden="1"/>
+    <row r="29" customFormat="1" hidden="1"/>
+    <row r="30" customFormat="1" hidden="1"/>
+    <row r="31" customFormat="1" hidden="1"/>
+    <row r="32" customFormat="1" hidden="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1198,9 +1304,9 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="47.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="22.86328125" customWidth="1"/>
-    <col min="3" max="3" width="54.33203125" customWidth="1"/>
-    <col min="4" max="4" width="77.46484375" customWidth="1"/>
+    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="3" max="3" width="54.3125" customWidth="1"/>
+    <col min="4" max="4" width="77.4375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="47.75" customHeight="1">
@@ -1393,15 +1499,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2795E5-0A07-4918-BFC6-ED555F7A394E}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.9296875" customWidth="1"/>
-    <col min="2" max="2" width="32.46484375" customWidth="1"/>
-    <col min="3" max="3" width="26.3984375" customWidth="1"/>
-    <col min="4" max="4" width="58.796875" customWidth="1"/>
+    <col min="1" max="1" width="8.9375" customWidth="1"/>
+    <col min="2" max="2" width="32.4375" customWidth="1"/>
+    <col min="3" max="3" width="26.375" customWidth="1"/>
+    <col min="4" max="4" width="58.8125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="13.9">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1514,15 +1620,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D2BBFF-A5A9-4621-A1B0-B5B41A144524}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" customWidth="1"/>
-    <col min="2" max="2" width="34.06640625" customWidth="1"/>
-    <col min="3" max="3" width="41.796875" customWidth="1"/>
-    <col min="4" max="4" width="47.53125" customWidth="1"/>
+    <col min="1" max="1" width="9.1875" customWidth="1"/>
+    <col min="2" max="2" width="34.0625" customWidth="1"/>
+    <col min="3" max="3" width="41.8125" customWidth="1"/>
+    <col min="4" max="4" width="47.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="13.9">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1655,14 +1761,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966BDC56-E696-48BC-BCCD-FDFD9FA85D73}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="30.3984375" customWidth="1"/>
-    <col min="4" max="4" width="44.59765625" customWidth="1"/>
+    <col min="2" max="2" width="36.3125" customWidth="1"/>
+    <col min="3" max="3" width="30.375" customWidth="1"/>
+    <col min="4" max="4" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="13.9">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1794,10 +1900,193 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B715C39C-22DE-467F-9455-0C85BBBA2363}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="41.9375" customWidth="1"/>
+    <col min="3" max="3" width="45.8125" customWidth="1"/>
+    <col min="4" max="4" width="44.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="27.75">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="89.25" customHeight="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="100.5" customHeight="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="88.5" customHeight="1">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="106.5" customHeight="1">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="70.5" customHeight="1">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="93.4" customHeight="1">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="90" customHeight="1">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="90" customHeight="1">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="90" customHeight="1">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="110.35" customHeight="1">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" ht="4.1500000000000004" customHeight="1"/>
+    <row r="22" hidden="1"/>
+    <row r="23" hidden="1"/>
+    <row r="24" hidden="1"/>
+    <row r="25" hidden="1"/>
+    <row r="26" hidden="1"/>
+    <row r="27" hidden="1"/>
+    <row r="28" hidden="1"/>
+    <row r="29" hidden="1"/>
+    <row r="30" hidden="1"/>
+    <row r="31" hidden="1"/>
+    <row r="32" hidden="1"/>
+    <row r="33" hidden="1"/>
+    <row r="34" hidden="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_NguyenHoanAnhQuan.xlsx
+++ b/AI Audit Log_NguyenHoanAnhQuan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUMMER2026\SWD392_SU26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7CA1C6-97EE-4921-8EEA-C28B59543728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34CDCFD-159B-48A5-A78C-D6B9FCFF0340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="7" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
@@ -19,8 +19,9 @@
     <sheet name="Week3.2" sheetId="5" r:id="rId4"/>
     <sheet name="Week4.1" sheetId="6" r:id="rId5"/>
     <sheet name="Week4.2" sheetId="7" r:id="rId6"/>
-    <sheet name="Week5" sheetId="8" r:id="rId7"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId8"/>
+    <sheet name="Week5." sheetId="4" r:id="rId7"/>
+    <sheet name="Week6" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,15 +37,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="182">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -620,19 +618,114 @@
     <t>Phản hồi: AI kiểm tra tính nhất quán giữa actor, object, message và luồng xử lý; phát hiện một số object chưa có trong Class Diagram và một số message không phù hợp với Main Flow.
 Kiểm chứng: Tôi đối chiếu lại với Use Case Specification và Class Diagram của nhóm.
 Quyết định: Chỉnh sửa Sequence Diagram trước khi hoàn thiện và nộp cho giảng viên.</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>State-dependent Dynamic Modeling</t>
+  </si>
+  <si>
+    <t>"State Diagram là gì và được sử dụng để làm gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích State Diagram mô tả các trạng thái của đối tượng và các sự kiện làm thay đổi trạng thái.
+Kiểm chứng: Tôi đối chiếu với slide bài học.
+Quyết định: Sử dụng State Diagram để mô hình hóa trạng thái của Ticket.</t>
+  </si>
+  <si>
+    <t>Xác định đối tượng</t>
+  </si>
+  <si>
+    <t>"Đối tượng nào trong Smart Queue Management System nên có State Diagram?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Ticket vì đối tượng này thay đổi trạng thái theo thời gian.
+Kiểm chứng: Đối chiếu với nghiệp vụ hệ thống.
+Quyết định: Chọn Ticket để xây dựng State Diagram.</t>
+  </si>
+  <si>
+    <t>Initial State</t>
+  </si>
+  <si>
+    <t>"Trạng thái ban đầu của Ticket là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất trạng thái Created sau khi khách hàng lấy số thứ tự.
+Kiểm chứng: So sánh với quy trình nghiệp vụ.
+Quyết định: Chọn Created là trạng thái đầu tiên.</t>
+  </si>
+  <si>
+    <t>State Identification</t>
+  </si>
+  <si>
+    <t>"Ticket có thể trải qua những trạng thái nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Created, Waiting, Called, Serving, Completed và Cancelled.
+Kiểm chứng: Đối chiếu với Use Case của nhóm.
+Quyết định: Áp dụng các trạng thái này vào sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Sự kiện nào làm Ticket chuyển từ Waiting sang Called?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác định sự kiện callNextTicket.
+Kiểm chứng: Đối chiếu với chức năng gọi số.
+Quyết định: Thêm event vào transition.</t>
+  </si>
+  <si>
+    <t>Transition</t>
+  </si>
+  <si>
+    <t>"Ticket chuyển từ Serving sang Completed khi nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất sự kiện finishService.
+Kiểm chứng: So sánh với quy trình phục vụ thực tế.
+Quyết định: Sử dụng transition này trong State Diagram.</t>
+  </si>
+  <si>
+    <t>Final State</t>
+  </si>
+  <si>
+    <t>"Trạng thái cuối cùng của Ticket là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết Ticket có thể kết thúc ở Completed hoặc Cancelled.
+Kiểm chứng: Đối chiếu với yêu cầu của hệ thống.
+Quyết định: Thiết kế hai trạng thái kết thúc.</t>
+  </si>
+  <si>
+    <t>Kiểm tra State Diagram</t>
+  </si>
+  <si>
+    <t>"Kiểm tra State Diagram của Ticket đã hợp lý chưa?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện thiếu transition từ Waiting sang Cancelled.
+Kiểm chứng: Đối chiếu với chức năng hủy hàng chờ.
+Quyết định: Bổ sung transition còn thiếu trước khi hoàn thiện sơ đồ.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -686,7 +779,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -700,7 +793,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -708,6 +801,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -718,11 +823,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1059,15 +1167,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.9375" customWidth="1"/>
-    <col min="2" max="2" width="26.875" customWidth="1"/>
-    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="1" max="1" width="20.9296875" customWidth="1"/>
+    <col min="2" max="2" width="26.86328125" customWidth="1"/>
+    <col min="3" max="3" width="24.265625" customWidth="1"/>
     <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.9">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1082,7 +1190,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="67.5">
+    <row r="2" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1096,7 +1204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="54">
+    <row r="3" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1110,7 +1218,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="67.5">
+    <row r="4" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1124,7 +1232,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="81">
+    <row r="5" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1146,14 +1254,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="41.9375" customWidth="1"/>
-    <col min="3" max="3" width="45.8125" customWidth="1"/>
-    <col min="4" max="4" width="44.875" customWidth="1"/>
+    <col min="2" max="2" width="41.9296875" customWidth="1"/>
+    <col min="3" max="3" width="45.796875" customWidth="1"/>
+    <col min="4" max="4" width="44.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.75">
+    <row r="1" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1167,7 +1275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="162" customHeight="1">
+    <row r="2" spans="1:4" ht="162" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1181,7 +1289,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="100.5" customHeight="1">
+    <row r="3" spans="1:4" ht="100.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1195,7 +1303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="145.9" customHeight="1">
+    <row r="4" spans="1:4" ht="145.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1209,7 +1317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="145.9" customHeight="1">
+    <row r="5" spans="1:4" ht="145.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1223,7 +1331,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="145.9" customHeight="1">
+    <row r="6" spans="1:4" ht="145.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1237,7 +1345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="145.9" customHeight="1">
+    <row r="7" spans="1:4" ht="145.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1251,7 +1359,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="145.9" customHeight="1">
+    <row r="8" spans="1:4" ht="145.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1265,7 +1373,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="213.4" customHeight="1">
+    <row r="9" spans="1:4" ht="213.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1279,20 +1387,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="4.1500000000000004" customHeight="1"/>
-    <row r="20" customFormat="1" hidden="1"/>
-    <row r="21" customFormat="1" hidden="1"/>
-    <row r="22" customFormat="1" hidden="1"/>
-    <row r="23" customFormat="1" hidden="1"/>
-    <row r="24" customFormat="1" hidden="1"/>
-    <row r="25" customFormat="1" hidden="1"/>
-    <row r="26" customFormat="1" hidden="1"/>
-    <row r="27" customFormat="1" hidden="1"/>
-    <row r="28" customFormat="1" hidden="1"/>
-    <row r="29" customFormat="1" hidden="1"/>
-    <row r="30" customFormat="1" hidden="1"/>
-    <row r="31" customFormat="1" hidden="1"/>
-    <row r="32" customFormat="1" hidden="1"/>
+    <row r="19" customFormat="1" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="20" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="21" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="22" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="23" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="24" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="25" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="26" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="27" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="28" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="29" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="30" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="31" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="32" customFormat="1" hidden="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1302,14 +1410,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="47.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="47.75" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="22.875" customWidth="1"/>
-    <col min="3" max="3" width="54.3125" customWidth="1"/>
-    <col min="4" max="4" width="77.4375" customWidth="1"/>
+    <col min="2" max="2" width="22.86328125" customWidth="1"/>
+    <col min="3" max="3" width="54.33203125" customWidth="1"/>
+    <col min="4" max="4" width="77.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="47.75" customHeight="1">
+    <row r="1" spans="1:4" ht="47.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1323,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="81.75" customHeight="1">
+    <row r="2" spans="1:4" ht="81.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1337,7 +1445,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="67.5" customHeight="1">
+    <row r="3" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1351,7 +1459,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="47.75" customHeight="1">
+    <row r="4" spans="1:4" ht="47.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1365,7 +1473,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="61.9" customHeight="1">
+    <row r="5" spans="1:4" ht="61.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1379,7 +1487,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="66" customHeight="1">
+    <row r="6" spans="1:4" ht="66" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1393,7 +1501,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="72.75" customHeight="1">
+    <row r="7" spans="1:4" ht="72.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1407,7 +1515,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="91.15" customHeight="1">
+    <row r="8" spans="1:4" ht="91.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1421,7 +1529,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="91.15" customHeight="1">
+    <row r="9" spans="1:4" ht="91.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1435,7 +1543,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="91.15" customHeight="1">
+    <row r="10" spans="1:4" ht="91.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1449,7 +1557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="91.15" customHeight="1">
+    <row r="11" spans="1:4" ht="91.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1463,7 +1571,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="91.15" customHeight="1">
+    <row r="12" spans="1:4" ht="91.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1477,7 +1585,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="77.25" customHeight="1">
+    <row r="13" spans="1:4" ht="77.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1499,15 +1607,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2795E5-0A07-4918-BFC6-ED555F7A394E}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.9375" customWidth="1"/>
-    <col min="2" max="2" width="32.4375" customWidth="1"/>
-    <col min="3" max="3" width="26.375" customWidth="1"/>
-    <col min="4" max="4" width="58.8125" customWidth="1"/>
+    <col min="1" max="1" width="8.9296875" customWidth="1"/>
+    <col min="2" max="2" width="32.46484375" customWidth="1"/>
+    <col min="3" max="3" width="26.3984375" customWidth="1"/>
+    <col min="4" max="4" width="58.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.9">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1521,7 +1629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="87" customHeight="1">
+    <row r="2" spans="1:4" ht="87" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1535,7 +1643,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="74.349999999999994" customHeight="1">
+    <row r="3" spans="1:4" ht="74.349999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1549,7 +1657,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="73.5" customHeight="1">
+    <row r="4" spans="1:4" ht="73.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1563,7 +1671,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="90" customHeight="1">
+    <row r="5" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1577,7 +1685,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="90" customHeight="1">
+    <row r="6" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1591,7 +1699,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="82.5" customHeight="1">
+    <row r="7" spans="1:4" ht="82.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1605,13 +1713,13 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="4.1500000000000004" customHeight="1"/>
-    <row r="12" spans="1:4" hidden="1"/>
-    <row r="13" spans="1:4" hidden="1"/>
-    <row r="14" spans="1:4" hidden="1"/>
-    <row r="15" spans="1:4" hidden="1"/>
-    <row r="16" spans="1:4" hidden="1"/>
-    <row r="17" hidden="1"/>
+    <row r="11" spans="1:4" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="17" hidden="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1620,15 +1728,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D2BBFF-A5A9-4621-A1B0-B5B41A144524}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1875" customWidth="1"/>
-    <col min="2" max="2" width="34.0625" customWidth="1"/>
-    <col min="3" max="3" width="41.8125" customWidth="1"/>
-    <col min="4" max="4" width="47.5625" customWidth="1"/>
+    <col min="1" max="1" width="9.19921875" customWidth="1"/>
+    <col min="2" max="2" width="34.06640625" customWidth="1"/>
+    <col min="3" max="3" width="41.796875" customWidth="1"/>
+    <col min="4" max="4" width="47.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.9">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1642,7 +1750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="118.25" customHeight="1">
+    <row r="2" spans="1:4" ht="118.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1656,7 +1764,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="134.35" customHeight="1">
+    <row r="3" spans="1:4" ht="134.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1670,7 +1778,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="96.4" customHeight="1">
+    <row r="4" spans="1:4" ht="96.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1684,7 +1792,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="96.4" customHeight="1">
+    <row r="5" spans="1:4" ht="96.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1698,7 +1806,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="96.4" customHeight="1">
+    <row r="6" spans="1:4" ht="96.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1712,7 +1820,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="96.4" customHeight="1">
+    <row r="7" spans="1:4" ht="96.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1726,7 +1834,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="96.4" customHeight="1">
+    <row r="8" spans="1:4" ht="96.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1740,19 +1848,19 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" ht="12.75" customHeight="1"/>
-    <row r="18" hidden="1"/>
-    <row r="19" hidden="1"/>
-    <row r="20" hidden="1"/>
-    <row r="21" hidden="1"/>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1"/>
-    <row r="24" hidden="1"/>
-    <row r="25" hidden="1"/>
-    <row r="26" hidden="1"/>
-    <row r="27" hidden="1"/>
-    <row r="28" hidden="1"/>
-    <row r="29" hidden="1"/>
+    <row r="17" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="18" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="19" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="20" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="21" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="22" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="23" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="24" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="25" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="26" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="27" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="28" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="29" hidden="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1761,14 +1869,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966BDC56-E696-48BC-BCCD-FDFD9FA85D73}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="36.3125" customWidth="1"/>
-    <col min="3" max="3" width="30.375" customWidth="1"/>
-    <col min="4" max="4" width="44.625" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" customWidth="1"/>
+    <col min="3" max="3" width="30.3984375" customWidth="1"/>
+    <col min="4" max="4" width="44.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.9">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1782,7 +1890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="107.65" customHeight="1">
+    <row r="2" spans="1:4" ht="107.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1796,7 +1904,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="108.75" customHeight="1">
+    <row r="3" spans="1:4" ht="108.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1810,7 +1918,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="118.5" customHeight="1">
+    <row r="4" spans="1:4" ht="118.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -1824,7 +1932,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="99.4" customHeight="1">
+    <row r="5" spans="1:4" ht="99.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1838,7 +1946,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="113.25" customHeight="1">
+    <row r="6" spans="1:4" ht="113.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1852,7 +1960,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="97.5" customHeight="1">
+    <row r="7" spans="1:4" ht="97.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -1866,7 +1974,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="88.5" customHeight="1">
+    <row r="8" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -1880,7 +1988,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="103.9" customHeight="1">
+    <row r="9" spans="1:4" ht="103.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1900,25 +2008,199 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B715C39C-22DE-467F-9455-0C85BBBA2363}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="41.9296875" customWidth="1"/>
+    <col min="3" max="3" width="45.796875" customWidth="1"/>
+    <col min="4" max="4" width="44.86328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="89.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="100.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="106.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="70.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="93.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="110.35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="22" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="23" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="24" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="25" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="26" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="27" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="28" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="29" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="30" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="31" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="32" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="33" hidden="1" x14ac:dyDescent="0.45"/>
+    <row r="34" hidden="1" x14ac:dyDescent="0.45"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B715C39C-22DE-467F-9455-0C85BBBA2363}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="41.9375" customWidth="1"/>
-    <col min="3" max="3" width="45.8125" customWidth="1"/>
-    <col min="4" max="4" width="44.875" customWidth="1"/>
+    <col min="2" max="2" width="38.46484375" customWidth="1"/>
+    <col min="3" max="3" width="32.1328125" customWidth="1"/>
+    <col min="4" max="4" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1928,165 +2210,132 @@
       <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="89.25" customHeight="1">
-      <c r="A2" s="2">
+    <row r="2" spans="1:4" ht="117.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="100.5" customHeight="1">
-      <c r="A3" s="2">
+      <c r="B2" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="87.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="88.5" customHeight="1">
-      <c r="A4" s="2">
+      <c r="B3" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="151.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="106.5" customHeight="1">
-      <c r="A5" s="2">
+      <c r="B4" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="91.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="70.5" customHeight="1">
-      <c r="A6" s="2">
+      <c r="B5" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="122.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="93.4" customHeight="1">
-      <c r="A7" s="2">
+      <c r="B6" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="138" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="90" customHeight="1">
-      <c r="A8" s="2">
+      <c r="B7" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="124.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="90" customHeight="1">
-      <c r="A9" s="2">
+      <c r="B8" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="172.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="90" customHeight="1">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="110.35" customHeight="1">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="21" ht="4.1500000000000004" customHeight="1"/>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1"/>
-    <row r="24" hidden="1"/>
-    <row r="25" hidden="1"/>
-    <row r="26" hidden="1"/>
-    <row r="27" hidden="1"/>
-    <row r="28" hidden="1"/>
-    <row r="29" hidden="1"/>
-    <row r="30" hidden="1"/>
-    <row r="31" hidden="1"/>
-    <row r="32" hidden="1"/>
-    <row r="33" hidden="1"/>
-    <row r="34" hidden="1"/>
+      <c r="B9" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>181</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3CB77D4-6C91-497B-A32A-4CDA41B9C790}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_NguyenHoanAnhQuan.xlsx
+++ b/AI Audit Log_NguyenHoanAnhQuan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUMMER2026\SWD392_SU26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34CDCFD-159B-48A5-A78C-D6B9FCFF0340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BD3A66-71B2-452C-ADBC-4E3CC06BCC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="7" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="2" activeTab="8" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,8 @@
     <sheet name="Week4.2" sheetId="7" r:id="rId6"/>
     <sheet name="Week5." sheetId="4" r:id="rId7"/>
     <sheet name="Week6" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId9"/>
+    <sheet name="Week7" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet2" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="205">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -706,19 +707,111 @@
     <t>Phản hồi: AI phát hiện thiếu transition từ Waiting sang Cancelled.
 Kiểm chứng: Đối chiếu với chức năng hủy hàng chờ.
 Quyết định: Bổ sung transition còn thiếu trước khi hoàn thiện sơ đồ.</t>
+  </si>
+  <si>
+    <t>Component Diagram</t>
+  </si>
+  <si>
+    <t>Xác định Component</t>
+  </si>
+  <si>
+    <t>Front-end Component</t>
+  </si>
+  <si>
+    <t>Backend Component</t>
+  </si>
+  <si>
+    <t>Database Component</t>
+  </si>
+  <si>
+    <t>Component Relationship</t>
+  </si>
+  <si>
+    <t>Kiểm tra Component Diagram</t>
+  </si>
+  <si>
+    <t>"Component Diagram là gì và được sử dụng trong giai đoạn nào của UML?"</t>
+  </si>
+  <si>
+    <t>"Đối với Smart Queue Management System Using AI, hệ thống nên có những component nào?"</t>
+  </si>
+  <si>
+    <t>"Frontend của hệ thống nên được biểu diễn như thế nào trong Component Diagram?"</t>
+  </si>
+  <si>
+    <t>"Backend nên chia thành những component nào?"</t>
+  </si>
+  <si>
+    <t>"AI Prediction Service có vai trò gì trong Component Diagram?"</t>
+  </si>
+  <si>
+    <t>"Database nên kết nối với những component nào?"</t>
+  </si>
+  <si>
+    <t>"Quan hệ giữa các component nên biểu diễn như thế nào?"</t>
+  </si>
+  <si>
+    <t>"Kiểm tra Component Diagram của nhóm đã hợp lý chưa?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện một số component có chức năng chồng chéo và đề xuất tách riêng AI Service khỏi Queue Service.
+Kiểm chứng: Tôi đối chiếu với kiến trúc hệ thống của nhóm.
+Quyết định: Điều chỉnh Component Diagram trước khi hoàn thiện tài liệu.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích các component được kết nối bằng dependency hoặc interface để thể hiện việc sử dụng dịch vụ của nhau.
+Kiểm chứng: Đối chiếu với ký hiệu UML Component Diagram.
+Quyết định: Áp dụng dependency giữa các component trong sơ đồ.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Database chỉ giao tiếp với các service ở backend thay vì kết nối trực tiếp với giao diện người dùng.
+Kiểm chứng: So sánh với kiến trúc nhiều lớp đã học.
+Quyết định: Thiết kế Database chỉ phục vụ backend</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích component này nhận dữ liệu hàng chờ và dự đoán thời gian chờ để gửi kết quả cho Queue Service.
+Kiểm chứng: Đối chiếu với chức năng AI của dự án.
+Quyết định: Thêm AI Prediction Service vào Component Diagram.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Queue Service, User Service, AI Service và Notification Service để tăng tính mô-đun.
+Kiểm chứng: Đối chiếu với kiến trúc backend của nhóm.
+Quyết định: Thiết kế backend theo các service độc lập.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất tách thành Mobile App và Admin Dashboard vì phục vụ hai nhóm người dùng khác nhau.
+Kiểm chứng: So sánh với yêu cầu của dự án.
+Quyết định: Tách Front-end thành hai component riêng.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các component như Mobile App, Web Dashboard, Queue Management Service, AI Prediction Service, Notification Service và Database.
+Kiểm chứng: Tôi đối chiếu với kiến trúc hệ thống mà nhóm đã xây dựng.
+Quyết định: Chọn các component phù hợp để đưa vào sơ đồ.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Component Diagram mô tả kiến trúc vật lý của hệ thống, thể hiện các module phần mềm và mối quan hệ giữa chúng.
+Kiểm chứng: Tôi đối chiếu với slide bài học về Component Diagram.
+Quyết định: Sử dụng Component Diagram để mô tả kiến trúc của dự án nhóm.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -779,7 +872,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -793,7 +886,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -801,6 +894,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -811,11 +916,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -823,13 +931,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1251,6 +1362,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C5A6E6-9E1B-49A9-BDF0-C04563B2EC06}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1:D32"/>
@@ -2333,9 +2453,142 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3CB77D4-6C91-497B-A32A-4CDA41B9C790}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="39.46484375" customWidth="1"/>
+    <col min="3" max="3" width="23.9296875" customWidth="1"/>
+    <col min="4" max="4" width="45.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="121.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="105.85" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="90.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="123" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="13">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="112.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="99.85" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="111" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="91.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="13">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/AI Audit Log_NguyenHoanAnhQuan.xlsx
+++ b/AI Audit Log_NguyenHoanAnhQuan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUMMER2026\SWD392_SU26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BD3A66-71B2-452C-ADBC-4E3CC06BCC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58546C67-02CB-4670-B8BE-AF0705DD97A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="2" activeTab="8" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="3" activeTab="9" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="Week5." sheetId="4" r:id="rId7"/>
     <sheet name="Week6" sheetId="8" r:id="rId8"/>
     <sheet name="Week7" sheetId="9" r:id="rId9"/>
-    <sheet name="Sheet2" sheetId="10" r:id="rId10"/>
+    <sheet name="Week8" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="229">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -792,19 +793,114 @@
     <t>Phản hồi: AI giải thích Component Diagram mô tả kiến trúc vật lý của hệ thống, thể hiện các module phần mềm và mối quan hệ giữa chúng.
 Kiểm chứng: Tôi đối chiếu với slide bài học về Component Diagram.
 Quyết định: Sử dụng Component Diagram để mô tả kiến trúc của dự án nhóm.</t>
+  </si>
+  <si>
+    <t>Project Introduction</t>
+  </si>
+  <si>
+    <t>"Hãy giúp tôi viết phần Introduction cho dự án Smart Queue Management System Using AI."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất nội dung giới thiệu về mục tiêu, bối cảnh và ý nghĩa của hệ thống quản lý hàng chờ tích hợp AI.
+Kiểm chứng: Tôi đối chiếu với ý tưởng dự án của nhóm.
+Quyết định: Chỉnh sửa nội dung để phù hợp với mục tiêu của nhóm.</t>
+  </si>
+  <si>
+    <t>Project Objectives</t>
+  </si>
+  <si>
+    <t>"Mục tiêu của dự án nên trình bày như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI gợi ý chia mục tiêu thành mục tiêu tổng quát và các mục tiêu cụ thể như giảm thời gian chờ, nâng cao trải nghiệm người dùng và tối ưu phân bổ quầy phục vụ.
+Kiểm chứng: So sánh với yêu cầu của giảng viên.
+Quyết định: Đưa các mục tiêu này vào báo cáo.</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>"Hãy giúp tôi viết phạm vi của dự án."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân chia phạm vi thành In Scope và Out of Scope, giúp xác định rõ chức năng của hệ thống.
+Kiểm chứng: Đối chiếu với Use Case Diagram của nhóm.
+Quyết định: Bổ sung phần Scope vào tài liệu.</t>
+  </si>
+  <si>
+    <t>Functional Requirements</t>
+  </si>
+  <si>
+    <t>"Liệt kê các Functional Requirements của hệ thống."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các chức năng như đăng nhập, lấy số thứ tự, xem trạng thái hàng chờ, gọi khách và gửi thông báo.
+Kiểm chứng: So sánh với Use Case đã xây dựng.
+Quyết định: Chỉnh sửa lại để thống nhất với phân tích của nhóm.</t>
+  </si>
+  <si>
+    <t>Non-functional Requirements</t>
+  </si>
+  <si>
+    <t>"Những Non-functional Requirements nào phù hợp với dự án?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI gợi ý các yêu cầu về hiệu năng, bảo mật, khả năng mở rộng và tính sẵn sàng của hệ thống.
+Kiểm chứng: Đối chiếu với nội dung môn học Software Engineering.
+Quyết định: Thêm các yêu cầu phi chức năng vào báo cáo.</t>
+  </si>
+  <si>
+    <t>Technology Stack</t>
+  </si>
+  <si>
+    <t>"Nên trình bày công nghệ sử dụng trong báo cáo như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất trình bày Frontend, Backend, Database và AI Service theo dạng bảng để dễ theo dõi.
+Kiểm chứng: So sánh với công nghệ nhóm đang sử dụng.
+Quyết định: Áp dụng cách trình bày này trong báo cáo.</t>
+  </si>
+  <si>
+    <t>Report Review</t>
+  </si>
+  <si>
+    <t>"Kiểm tra giúp tôi phần nội dung báo cáo đã logic và đầy đủ chưa."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện một số mục còn thiếu và đề xuất bổ sung phần Assumptions và Constraints.
+Kiểm chứng: Đối chiếu với mẫu báo cáo do giảng viên cung cấp.
+Quyết định: Bổ sung các mục còn thiếu trước khi hoàn thiện báo cáo.</t>
+  </si>
+  <si>
+    <t>Grammar &amp; Formatting</t>
+  </si>
+  <si>
+    <t>"Kiểm tra lỗi chính tả và cách trình bày tài liệu báo cáo."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sửa lỗi ngữ pháp tiếng Anh, thống nhất cách viết tiêu đề và định dạng các mục.
+Kiểm chứng: Tôi đọc lại toàn bộ tài liệu sau khi chỉnh sửa.
+Quyết định: Sử dụng phiên bản đã chỉnh sửa để đưa vào báo cáo cuối cùng.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -872,7 +968,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -886,7 +982,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -894,6 +990,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -904,11 +1012,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -916,32 +1027,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1364,6 +1466,147 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C5A6E6-9E1B-49A9-BDF0-C04563B2EC06}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="23.59765625" customWidth="1"/>
+    <col min="3" max="3" width="26.1328125" customWidth="1"/>
+    <col min="4" max="4" width="51.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A2" s="24">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A3" s="24">
+        <v>2</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A4" s="24">
+        <v>3</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A5" s="24">
+        <v>4</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A6" s="24">
+        <v>5</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A7" s="24">
+        <v>6</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A8" s="24">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A9" s="13">
+        <v>8</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F7F31F-B71E-45A6-A17A-82033017C3A6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
